--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095089</v>
+        <v>124095058</v>
       </c>
       <c r="B2" t="n">
-        <v>74691</v>
+        <v>78108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095080</v>
+        <v>124095089</v>
       </c>
       <c r="B3" t="n">
-        <v>79804</v>
+        <v>74691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -957,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095058</v>
+        <v>124095073</v>
       </c>
       <c r="B4" t="n">
-        <v>78108</v>
+        <v>74887</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,25 +973,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>1469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1098,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124095073</v>
+        <v>124095080</v>
       </c>
       <c r="B5" t="n">
-        <v>74887</v>
+        <v>79804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,37 +1118,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1469</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095073</v>
+        <v>124095089</v>
       </c>
       <c r="B2" t="n">
-        <v>74909</v>
+        <v>74713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1469</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -965,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095089</v>
+        <v>124095080</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>79826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,21 +973,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1106,10 +1098,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124095080</v>
+        <v>124095073</v>
       </c>
       <c r="B5" t="n">
-        <v>79826</v>
+        <v>74909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,29 +1110,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>1469</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095089</v>
+        <v>124095080</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
+        <v>79826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095058</v>
+        <v>124095073</v>
       </c>
       <c r="B3" t="n">
-        <v>78130</v>
+        <v>74909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>1469</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -957,10 +965,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095080</v>
+        <v>124095089</v>
       </c>
       <c r="B4" t="n">
-        <v>79826</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,21 +981,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1098,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124095073</v>
+        <v>124095058</v>
       </c>
       <c r="B5" t="n">
-        <v>74909</v>
+        <v>78130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,33 +1122,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1469</v>
+        <v>145</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>J.Lahm ex Körb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095080</v>
+        <v>124095058</v>
       </c>
       <c r="B2" t="n">
-        <v>79826</v>
+        <v>78130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095073</v>
+        <v>124095089</v>
       </c>
       <c r="B3" t="n">
-        <v>74909</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +828,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1469</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -965,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095089</v>
+        <v>124095073</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>74909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,29 +969,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>1469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124095058</v>
+        <v>124095080</v>
       </c>
       <c r="B5" t="n">
-        <v>78130</v>
+        <v>79826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>145</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095058</v>
+        <v>124095073</v>
       </c>
       <c r="B2" t="n">
-        <v>78130</v>
+        <v>74909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>1469</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -957,10 +965,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095073</v>
+        <v>124095058</v>
       </c>
       <c r="B4" t="n">
-        <v>74909</v>
+        <v>78130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,33 +981,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1469</v>
+        <v>145</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>J.Lahm ex Körb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095073</v>
+        <v>124095089</v>
       </c>
       <c r="B2" t="n">
-        <v>74909</v>
+        <v>74713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1469</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -824,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095089</v>
+        <v>124095073</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>74909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,29 +828,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>1469</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095089</v>
+        <v>124095073</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
+        <v>74909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>1469</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -816,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095073</v>
+        <v>124095080</v>
       </c>
       <c r="B3" t="n">
-        <v>74909</v>
+        <v>79826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +836,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1469</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124095080</v>
+        <v>124095089</v>
       </c>
       <c r="B5" t="n">
-        <v>79826</v>
+        <v>74713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124095073</v>
+        <v>124095058</v>
       </c>
       <c r="B2" t="n">
-        <v>74909</v>
+        <v>78130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1469</v>
+        <v>145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>J.Lahm ex Körb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -824,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095080</v>
+        <v>124095089</v>
       </c>
       <c r="B3" t="n">
-        <v>79826</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,21 +832,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -965,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095058</v>
+        <v>124095073</v>
       </c>
       <c r="B4" t="n">
-        <v>78130</v>
+        <v>74909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,25 +973,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>1469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1106,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124095089</v>
+        <v>124095080</v>
       </c>
       <c r="B5" t="n">
-        <v>74713</v>
+        <v>79826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>124095058</v>
       </c>
       <c r="B2" t="n">
-        <v>78130</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,41 +811,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124095089</v>
+        <v>124095073</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>1469</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -957,49 +955,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124095073</v>
+        <v>124095089</v>
       </c>
       <c r="B4" t="n">
-        <v>74909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1469</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten blekspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora peronella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1109,12 +1094,7 @@
         <v>124095080</v>
       </c>
       <c r="B5" t="n">
-        <v>79826</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31138-2023 artfynd.xlsx
+++ b/artfynd/A 31138-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124095058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -952,6 +962,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124095073</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1088,6 +1103,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124095089</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1224,8 +1244,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124095080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>